--- a/wwwroot/plantilla_equipos.xlsx
+++ b/wwwroot/plantilla_equipos.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipos" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Referencia" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Equipos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Referencia" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -828,8 +828,8 @@
     <mergeCell ref="A1:N1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="B5:B24" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Tipo inválido" error="Valor no válido. Use: Laptop, Teléfono, Tablet u Otro" type="list">
-      <formula1>"Laptop,Teléfono,Tablet,Otro"</formula1>
+    <dataValidation sqref="B5:B24" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Tipo inválido" error="Valor no válido. Use: Laptop, Celular, Tablet u Otro" type="list">
+      <formula1>"Laptop,Celular,Tablet,Otro"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -866,7 +866,7 @@
     <row r="3">
       <c r="A3" s="11" t="inlineStr">
         <is>
-          <t>Teléfono</t>
+          <t>Celular</t>
         </is>
       </c>
     </row>

--- a/wwwroot/plantilla_equipos.xlsx
+++ b/wwwroot/plantilla_equipos.xlsx
@@ -154,9 +154,7 @@
     <xf numFmtId="164" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -534,10 +532,11 @@
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="28" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -583,20 +582,25 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
+          <t>IMEI</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
           <t>Accesorios</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>Costo</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>FechaCompra</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>FechaGarantia</t>
         </is>
@@ -609,9 +613,10 @@
       <c r="D5" s="4" t="n"/>
       <c r="E5" s="4" t="n"/>
       <c r="F5" s="4" t="n"/>
-      <c r="G5" s="5" t="n"/>
-      <c r="H5" s="6" t="n"/>
+      <c r="G5" s="4" t="n"/>
+      <c r="H5" s="5" t="n"/>
       <c r="I5" s="6" t="n"/>
+      <c r="J5" s="6" t="n"/>
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="7" t="n"/>
@@ -620,9 +625,10 @@
       <c r="D6" s="7" t="n"/>
       <c r="E6" s="7" t="n"/>
       <c r="F6" s="7" t="n"/>
-      <c r="G6" s="8" t="n"/>
-      <c r="H6" s="9" t="n"/>
+      <c r="G6" s="7" t="n"/>
+      <c r="H6" s="8" t="n"/>
       <c r="I6" s="9" t="n"/>
+      <c r="J6" s="9" t="n"/>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="4" t="n"/>
@@ -631,9 +637,10 @@
       <c r="D7" s="4" t="n"/>
       <c r="E7" s="4" t="n"/>
       <c r="F7" s="4" t="n"/>
-      <c r="G7" s="5" t="n"/>
-      <c r="H7" s="6" t="n"/>
+      <c r="G7" s="4" t="n"/>
+      <c r="H7" s="5" t="n"/>
       <c r="I7" s="6" t="n"/>
+      <c r="J7" s="6" t="n"/>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="7" t="n"/>
@@ -642,9 +649,10 @@
       <c r="D8" s="7" t="n"/>
       <c r="E8" s="7" t="n"/>
       <c r="F8" s="7" t="n"/>
-      <c r="G8" s="8" t="n"/>
-      <c r="H8" s="9" t="n"/>
+      <c r="G8" s="7" t="n"/>
+      <c r="H8" s="8" t="n"/>
       <c r="I8" s="9" t="n"/>
+      <c r="J8" s="9" t="n"/>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="4" t="n"/>
@@ -653,9 +661,10 @@
       <c r="D9" s="4" t="n"/>
       <c r="E9" s="4" t="n"/>
       <c r="F9" s="4" t="n"/>
-      <c r="G9" s="5" t="n"/>
-      <c r="H9" s="6" t="n"/>
+      <c r="G9" s="4" t="n"/>
+      <c r="H9" s="5" t="n"/>
       <c r="I9" s="6" t="n"/>
+      <c r="J9" s="6" t="n"/>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="7" t="n"/>
@@ -664,9 +673,10 @@
       <c r="D10" s="7" t="n"/>
       <c r="E10" s="7" t="n"/>
       <c r="F10" s="7" t="n"/>
-      <c r="G10" s="8" t="n"/>
-      <c r="H10" s="9" t="n"/>
+      <c r="G10" s="7" t="n"/>
+      <c r="H10" s="8" t="n"/>
       <c r="I10" s="9" t="n"/>
+      <c r="J10" s="9" t="n"/>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="4" t="n"/>
@@ -675,9 +685,10 @@
       <c r="D11" s="4" t="n"/>
       <c r="E11" s="4" t="n"/>
       <c r="F11" s="4" t="n"/>
-      <c r="G11" s="5" t="n"/>
-      <c r="H11" s="6" t="n"/>
+      <c r="G11" s="4" t="n"/>
+      <c r="H11" s="5" t="n"/>
       <c r="I11" s="6" t="n"/>
+      <c r="J11" s="6" t="n"/>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="7" t="n"/>
@@ -686,9 +697,10 @@
       <c r="D12" s="7" t="n"/>
       <c r="E12" s="7" t="n"/>
       <c r="F12" s="7" t="n"/>
-      <c r="G12" s="8" t="n"/>
-      <c r="H12" s="9" t="n"/>
+      <c r="G12" s="7" t="n"/>
+      <c r="H12" s="8" t="n"/>
       <c r="I12" s="9" t="n"/>
+      <c r="J12" s="9" t="n"/>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="4" t="n"/>
@@ -697,9 +709,10 @@
       <c r="D13" s="4" t="n"/>
       <c r="E13" s="4" t="n"/>
       <c r="F13" s="4" t="n"/>
-      <c r="G13" s="5" t="n"/>
-      <c r="H13" s="6" t="n"/>
+      <c r="G13" s="4" t="n"/>
+      <c r="H13" s="5" t="n"/>
       <c r="I13" s="6" t="n"/>
+      <c r="J13" s="6" t="n"/>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="7" t="n"/>
@@ -708,9 +721,10 @@
       <c r="D14" s="7" t="n"/>
       <c r="E14" s="7" t="n"/>
       <c r="F14" s="7" t="n"/>
-      <c r="G14" s="8" t="n"/>
-      <c r="H14" s="9" t="n"/>
+      <c r="G14" s="7" t="n"/>
+      <c r="H14" s="8" t="n"/>
       <c r="I14" s="9" t="n"/>
+      <c r="J14" s="9" t="n"/>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="4" t="n"/>
@@ -719,9 +733,10 @@
       <c r="D15" s="4" t="n"/>
       <c r="E15" s="4" t="n"/>
       <c r="F15" s="4" t="n"/>
-      <c r="G15" s="5" t="n"/>
-      <c r="H15" s="6" t="n"/>
+      <c r="G15" s="4" t="n"/>
+      <c r="H15" s="5" t="n"/>
       <c r="I15" s="6" t="n"/>
+      <c r="J15" s="6" t="n"/>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="7" t="n"/>
@@ -730,9 +745,10 @@
       <c r="D16" s="7" t="n"/>
       <c r="E16" s="7" t="n"/>
       <c r="F16" s="7" t="n"/>
-      <c r="G16" s="8" t="n"/>
-      <c r="H16" s="9" t="n"/>
+      <c r="G16" s="7" t="n"/>
+      <c r="H16" s="8" t="n"/>
       <c r="I16" s="9" t="n"/>
+      <c r="J16" s="9" t="n"/>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="4" t="n"/>
@@ -741,9 +757,10 @@
       <c r="D17" s="4" t="n"/>
       <c r="E17" s="4" t="n"/>
       <c r="F17" s="4" t="n"/>
-      <c r="G17" s="5" t="n"/>
-      <c r="H17" s="6" t="n"/>
+      <c r="G17" s="4" t="n"/>
+      <c r="H17" s="5" t="n"/>
       <c r="I17" s="6" t="n"/>
+      <c r="J17" s="6" t="n"/>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="7" t="n"/>
@@ -752,9 +769,10 @@
       <c r="D18" s="7" t="n"/>
       <c r="E18" s="7" t="n"/>
       <c r="F18" s="7" t="n"/>
-      <c r="G18" s="8" t="n"/>
-      <c r="H18" s="9" t="n"/>
+      <c r="G18" s="7" t="n"/>
+      <c r="H18" s="8" t="n"/>
       <c r="I18" s="9" t="n"/>
+      <c r="J18" s="9" t="n"/>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="4" t="n"/>
@@ -763,9 +781,10 @@
       <c r="D19" s="4" t="n"/>
       <c r="E19" s="4" t="n"/>
       <c r="F19" s="4" t="n"/>
-      <c r="G19" s="5" t="n"/>
-      <c r="H19" s="6" t="n"/>
+      <c r="G19" s="4" t="n"/>
+      <c r="H19" s="5" t="n"/>
       <c r="I19" s="6" t="n"/>
+      <c r="J19" s="6" t="n"/>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="7" t="n"/>
@@ -774,9 +793,10 @@
       <c r="D20" s="7" t="n"/>
       <c r="E20" s="7" t="n"/>
       <c r="F20" s="7" t="n"/>
-      <c r="G20" s="8" t="n"/>
-      <c r="H20" s="9" t="n"/>
+      <c r="G20" s="7" t="n"/>
+      <c r="H20" s="8" t="n"/>
       <c r="I20" s="9" t="n"/>
+      <c r="J20" s="9" t="n"/>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="4" t="n"/>
@@ -785,9 +805,10 @@
       <c r="D21" s="4" t="n"/>
       <c r="E21" s="4" t="n"/>
       <c r="F21" s="4" t="n"/>
-      <c r="G21" s="5" t="n"/>
-      <c r="H21" s="6" t="n"/>
+      <c r="G21" s="4" t="n"/>
+      <c r="H21" s="5" t="n"/>
       <c r="I21" s="6" t="n"/>
+      <c r="J21" s="6" t="n"/>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="7" t="n"/>
@@ -796,9 +817,10 @@
       <c r="D22" s="7" t="n"/>
       <c r="E22" s="7" t="n"/>
       <c r="F22" s="7" t="n"/>
-      <c r="G22" s="8" t="n"/>
-      <c r="H22" s="9" t="n"/>
+      <c r="G22" s="7" t="n"/>
+      <c r="H22" s="8" t="n"/>
       <c r="I22" s="9" t="n"/>
+      <c r="J22" s="9" t="n"/>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="4" t="n"/>
@@ -807,9 +829,10 @@
       <c r="D23" s="4" t="n"/>
       <c r="E23" s="4" t="n"/>
       <c r="F23" s="4" t="n"/>
-      <c r="G23" s="5" t="n"/>
-      <c r="H23" s="6" t="n"/>
+      <c r="G23" s="4" t="n"/>
+      <c r="H23" s="5" t="n"/>
       <c r="I23" s="6" t="n"/>
+      <c r="J23" s="6" t="n"/>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="7" t="n"/>
@@ -818,9 +841,10 @@
       <c r="D24" s="7" t="n"/>
       <c r="E24" s="7" t="n"/>
       <c r="F24" s="7" t="n"/>
-      <c r="G24" s="8" t="n"/>
-      <c r="H24" s="9" t="n"/>
+      <c r="G24" s="7" t="n"/>
+      <c r="H24" s="8" t="n"/>
       <c r="I24" s="9" t="n"/>
+      <c r="J24" s="9" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -828,7 +852,7 @@
     <mergeCell ref="A1:N1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="B5:B24" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Tipo inválido" error="Valor no válido. Use: Laptop, Celular, Tablet u Otro" type="list">
+    <dataValidation sqref="B5:B24" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Tipo inválido" error="Valor no válido. Use: Laptop, Celular, Tablet u Otro" type="list">
       <formula1>"Laptop,Celular,Tablet,Otro"</formula1>
     </dataValidation>
   </dataValidations>
@@ -842,7 +866,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:A14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -927,9 +951,6 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:B1"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/wwwroot/plantilla_equipos.xlsx
+++ b/wwwroot/plantilla_equipos.xlsx
@@ -524,7 +524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N24"/>
+  <dimension ref="A1:O24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -537,6 +537,7 @@
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -603,6 +604,11 @@
       <c r="J4" s="3" t="inlineStr">
         <is>
           <t>FechaGarantia</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>CodigoActivoFijo</t>
         </is>
       </c>
     </row>
@@ -617,6 +623,7 @@
       <c r="H5" s="5" t="n"/>
       <c r="I5" s="6" t="n"/>
       <c r="J5" s="6" t="n"/>
+      <c r="K5" s="4" t="n"/>
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="7" t="n"/>
@@ -629,6 +636,7 @@
       <c r="H6" s="8" t="n"/>
       <c r="I6" s="9" t="n"/>
       <c r="J6" s="9" t="n"/>
+      <c r="K6" s="7" t="n"/>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="4" t="n"/>
@@ -641,6 +649,7 @@
       <c r="H7" s="5" t="n"/>
       <c r="I7" s="6" t="n"/>
       <c r="J7" s="6" t="n"/>
+      <c r="K7" s="4" t="n"/>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="7" t="n"/>
@@ -653,6 +662,7 @@
       <c r="H8" s="8" t="n"/>
       <c r="I8" s="9" t="n"/>
       <c r="J8" s="9" t="n"/>
+      <c r="K8" s="7" t="n"/>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="4" t="n"/>
@@ -665,6 +675,7 @@
       <c r="H9" s="5" t="n"/>
       <c r="I9" s="6" t="n"/>
       <c r="J9" s="6" t="n"/>
+      <c r="K9" s="4" t="n"/>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="7" t="n"/>
@@ -677,6 +688,7 @@
       <c r="H10" s="8" t="n"/>
       <c r="I10" s="9" t="n"/>
       <c r="J10" s="9" t="n"/>
+      <c r="K10" s="7" t="n"/>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="4" t="n"/>
@@ -689,6 +701,7 @@
       <c r="H11" s="5" t="n"/>
       <c r="I11" s="6" t="n"/>
       <c r="J11" s="6" t="n"/>
+      <c r="K11" s="4" t="n"/>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="7" t="n"/>
@@ -701,6 +714,7 @@
       <c r="H12" s="8" t="n"/>
       <c r="I12" s="9" t="n"/>
       <c r="J12" s="9" t="n"/>
+      <c r="K12" s="7" t="n"/>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="4" t="n"/>
@@ -713,6 +727,7 @@
       <c r="H13" s="5" t="n"/>
       <c r="I13" s="6" t="n"/>
       <c r="J13" s="6" t="n"/>
+      <c r="K13" s="4" t="n"/>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="7" t="n"/>
@@ -725,6 +740,7 @@
       <c r="H14" s="8" t="n"/>
       <c r="I14" s="9" t="n"/>
       <c r="J14" s="9" t="n"/>
+      <c r="K14" s="7" t="n"/>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="4" t="n"/>
@@ -737,6 +753,7 @@
       <c r="H15" s="5" t="n"/>
       <c r="I15" s="6" t="n"/>
       <c r="J15" s="6" t="n"/>
+      <c r="K15" s="4" t="n"/>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="7" t="n"/>
@@ -749,6 +766,7 @@
       <c r="H16" s="8" t="n"/>
       <c r="I16" s="9" t="n"/>
       <c r="J16" s="9" t="n"/>
+      <c r="K16" s="7" t="n"/>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="4" t="n"/>
@@ -761,6 +779,7 @@
       <c r="H17" s="5" t="n"/>
       <c r="I17" s="6" t="n"/>
       <c r="J17" s="6" t="n"/>
+      <c r="K17" s="4" t="n"/>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="7" t="n"/>
@@ -773,6 +792,7 @@
       <c r="H18" s="8" t="n"/>
       <c r="I18" s="9" t="n"/>
       <c r="J18" s="9" t="n"/>
+      <c r="K18" s="7" t="n"/>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="4" t="n"/>
@@ -785,6 +805,7 @@
       <c r="H19" s="5" t="n"/>
       <c r="I19" s="6" t="n"/>
       <c r="J19" s="6" t="n"/>
+      <c r="K19" s="4" t="n"/>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="7" t="n"/>
@@ -797,6 +818,7 @@
       <c r="H20" s="8" t="n"/>
       <c r="I20" s="9" t="n"/>
       <c r="J20" s="9" t="n"/>
+      <c r="K20" s="7" t="n"/>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="4" t="n"/>
@@ -809,6 +831,7 @@
       <c r="H21" s="5" t="n"/>
       <c r="I21" s="6" t="n"/>
       <c r="J21" s="6" t="n"/>
+      <c r="K21" s="4" t="n"/>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="7" t="n"/>
@@ -821,6 +844,7 @@
       <c r="H22" s="8" t="n"/>
       <c r="I22" s="9" t="n"/>
       <c r="J22" s="9" t="n"/>
+      <c r="K22" s="7" t="n"/>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="4" t="n"/>
@@ -833,6 +857,7 @@
       <c r="H23" s="5" t="n"/>
       <c r="I23" s="6" t="n"/>
       <c r="J23" s="6" t="n"/>
+      <c r="K23" s="4" t="n"/>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="7" t="n"/>
@@ -845,11 +870,12 @@
       <c r="H24" s="8" t="n"/>
       <c r="I24" s="9" t="n"/>
       <c r="J24" s="9" t="n"/>
+      <c r="K24" s="7" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:N2"/>
-    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="A2:O2"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="B5:B24" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Tipo inválido" error="Valor no válido. Use: Laptop, Celular, Tablet u Otro" type="list">
